--- a/resources/dierenkliniek.xlsx
+++ b/resources/dierenkliniek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\studieboeken\leeraccess\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BA0C68-8C4E-4F6C-8A4D-001DFE6F3ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC1DD67-9A7E-48CE-AC14-4FB3381389F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{BCB87582-9A87-4DDC-AD78-8CFA87B3BFB0}"/>
   </bookViews>
@@ -140,17 +140,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -465,199 +464,193 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0DD9FE1-B8F5-44E5-B6F9-64856BD41D18}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="B2:H14"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="2"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="2">
         <v>123</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E3" s="2">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5">
-        <v>42375</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="G3" s="4">
+        <v>45297</v>
+      </c>
+      <c r="H3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="F3" s="5">
-        <v>42454</v>
-      </c>
-      <c r="G3" s="2" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="G4" s="4">
+        <v>45376</v>
+      </c>
+      <c r="H4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="F4" s="5">
-        <v>42466</v>
-      </c>
-      <c r="G4" s="2" t="s">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="G5" s="4">
+        <v>45388</v>
+      </c>
+      <c r="H5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
         <v>149</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="2">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="5">
-        <v>42390</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="4">
+        <v>45312</v>
+      </c>
+      <c r="H7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="F8" s="5">
-        <v>42444</v>
-      </c>
-      <c r="G8" s="2" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="G8" s="4">
+        <v>45366</v>
+      </c>
+      <c r="H8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
         <v>170</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="3">
+      <c r="E10" s="2">
         <v>4</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="5">
-        <v>42046</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="4">
+        <v>45333</v>
+      </c>
+      <c r="H10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="F11" s="5">
-        <v>42418</v>
-      </c>
-      <c r="G11" s="2" t="s">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="G11" s="4">
+        <v>45340</v>
+      </c>
+      <c r="H11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
         <v>260</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3">
+      <c r="E13" s="2">
         <v>2</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="5">
-        <v>42487</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="4">
+        <v>45409</v>
+      </c>
+      <c r="H13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F14" s="5">
-        <v>42487</v>
-      </c>
-      <c r="G14" s="2" t="s">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G14" s="4">
+        <v>45409</v>
+      </c>
+      <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
